--- a/results/detailed_report_spa2.xlsx
+++ b/results/detailed_report_spa2.xlsx
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.324229975138252e-09</v>
+        <v>5.324229974988158e-09</v>
       </c>
       <c r="E2" t="n">
         <v>240</v>
       </c>
       <c r="F2" t="n">
-        <v>1.689453500000127</v>
+        <v>0.9726895000021614</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.570738981572361e-09</v>
+        <v>5.570738981843445e-09</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2993876000000455</v>
+        <v>0.3076309999996738</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.93781410636293e-08</v>
+        <v>6.937814105275417e-08</v>
       </c>
       <c r="E4" t="n">
         <v>8285</v>
       </c>
       <c r="F4" t="n">
-        <v>62.75721389999944</v>
+        <v>31.41149170000062</v>
       </c>
     </row>
     <row r="5">
@@ -539,13 +539,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4842725773822e-09</v>
+        <v>1.484272576529896e-09</v>
       </c>
       <c r="E5" t="n">
         <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>6.687324499999704</v>
+        <v>4.80463840000084</v>
       </c>
     </row>
     <row r="6">
@@ -561,13 +561,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.58666060301418e-07</v>
+        <v>5.58666060323775e-07</v>
       </c>
       <c r="E6" t="n">
         <v>196</v>
       </c>
       <c r="F6" t="n">
-        <v>1.811751500000355</v>
+        <v>0.7991468000000168</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.794322029402295e-07</v>
+        <v>2.794322030817201e-07</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2324294999998529</v>
+        <v>0.2385383000000729</v>
       </c>
     </row>
     <row r="8">
@@ -605,13 +605,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>6.865240116795568e-06</v>
+        <v>6.8652401167873e-06</v>
       </c>
       <c r="E8" t="n">
         <v>5087</v>
       </c>
       <c r="F8" t="n">
-        <v>38.77415930000006</v>
+        <v>19.33992669999861</v>
       </c>
     </row>
     <row r="9">
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.572869888198515e-07</v>
+        <v>1.572869890250294e-07</v>
       </c>
       <c r="E9" t="n">
         <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>5.243911900000057</v>
+        <v>3.832183499998791</v>
       </c>
     </row>
     <row r="10">
@@ -649,13 +649,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001197984617855757</v>
+        <v>0.0001197984617855643</v>
       </c>
       <c r="E10" t="n">
         <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8955988999996407</v>
+        <v>0.5075418999986141</v>
       </c>
     </row>
     <row r="11">
@@ -671,13 +671,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.141641259527471e-05</v>
+        <v>5.14164125952756e-05</v>
       </c>
       <c r="E11" t="n">
         <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.160427200000413</v>
+        <v>0.1643644000032509</v>
       </c>
     </row>
     <row r="12">
@@ -693,13 +693,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0006694229253856877</v>
+        <v>0.000669422925385688</v>
       </c>
       <c r="E12" t="n">
         <v>1949</v>
       </c>
       <c r="F12" t="n">
-        <v>15.49612439999964</v>
+        <v>7.403228099999978</v>
       </c>
     </row>
     <row r="13">
@@ -715,13 +715,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.666756136672059e-05</v>
+        <v>1.666756136669678e-05</v>
       </c>
       <c r="E13" t="n">
         <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>3.992202600000383</v>
+        <v>2.74356820000321</v>
       </c>
     </row>
     <row r="14">
@@ -737,13 +737,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.009821128457264048</v>
+        <v>0.009821128457264065</v>
       </c>
       <c r="E14" t="n">
         <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3034475999993447</v>
+        <v>0.1825482000022021</v>
       </c>
     </row>
     <row r="15">
@@ -759,13 +759,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002598895587452195</v>
+        <v>0.002598895587452194</v>
       </c>
       <c r="E15" t="n">
         <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1037894000000961</v>
+        <v>0.09199470000021392</v>
       </c>
     </row>
     <row r="16">
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01812964511711219</v>
+        <v>0.01812964511711221</v>
       </c>
       <c r="E16" t="n">
         <v>161</v>
       </c>
       <c r="F16" t="n">
-        <v>1.184615199999826</v>
+        <v>0.6662394000013592</v>
       </c>
     </row>
     <row r="17">
@@ -803,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001766246519114123</v>
+        <v>0.001766246519114165</v>
       </c>
       <c r="E17" t="n">
         <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>2.471290899999985</v>
+        <v>1.773163699999714</v>
       </c>
     </row>
   </sheetData>

--- a/results/detailed_report_spa2.xlsx
+++ b/results/detailed_report_spa2.xlsx
@@ -479,7 +479,7 @@
         <v>240</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9726895000021614</v>
+        <v>1.148875000000771</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3076309999996738</v>
+        <v>0.333852100000513</v>
       </c>
     </row>
     <row r="4">
@@ -523,7 +523,7 @@
         <v>8285</v>
       </c>
       <c r="F4" t="n">
-        <v>31.41149170000062</v>
+        <v>36.15682819999893</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>4.80463840000084</v>
+        <v>5.411553800000547</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>196</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7991468000000168</v>
+        <v>0.8088499000004958</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2385383000000729</v>
+        <v>0.3193031999999221</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         <v>5087</v>
       </c>
       <c r="F8" t="n">
-        <v>19.33992669999861</v>
+        <v>21.34596299999976</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +633,7 @@
         <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>3.832183499998791</v>
+        <v>4.368895800000246</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5075418999986141</v>
+        <v>0.5465192999999999</v>
       </c>
     </row>
     <row r="11">
@@ -677,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1643644000032509</v>
+        <v>0.1773796000015864</v>
       </c>
     </row>
     <row r="12">
@@ -699,7 +699,7 @@
         <v>1949</v>
       </c>
       <c r="F12" t="n">
-        <v>7.403228099999978</v>
+        <v>7.994186199999604</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
         <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>2.74356820000321</v>
+        <v>3.05886019999889</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         <v>42</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1825482000022021</v>
+        <v>0.1983187999994698</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09199470000021392</v>
+        <v>0.1021783000014693</v>
       </c>
     </row>
     <row r="16">
@@ -787,7 +787,7 @@
         <v>161</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6662394000013592</v>
+        <v>0.7030422999996517</v>
       </c>
     </row>
     <row r="17">
@@ -809,7 +809,7 @@
         <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>1.773163699999714</v>
+        <v>2.035874499999409</v>
       </c>
     </row>
   </sheetData>
